--- a/RequestData.xlsx
+++ b/RequestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\E-work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\Thefirst-E-work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A96B624-DC34-453B-BCC2-84F6C0DD3A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2120DB0-7678-4AE7-8DE6-72955861EF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7830" yWindow="2490" windowWidth="21600" windowHeight="11295" xr2:uid="{799AF58B-C093-4573-81AA-7B94D8971B9B}"/>
+    <workbookView xWindow="5730" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{799AF58B-C093-4573-81AA-7B94D8971B9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>ลำดับ</t>
   </si>
@@ -42,9 +42,6 @@
     <t>PASSPORT NUMBER</t>
   </si>
   <si>
-    <t>PYAY NYEIN</t>
-  </si>
-  <si>
     <t>MH295863</t>
   </si>
   <si>
@@ -57,16 +54,19 @@
     <t>MH295866</t>
   </si>
   <si>
-    <t>MH295867</t>
-  </si>
-  <si>
-    <t>MH295868</t>
-  </si>
-  <si>
-    <t>MH295869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	69155200178628</t>
+    <t>Amdhr1688@gmail.com</t>
+  </si>
+  <si>
+    <t>PYAY NYEIN 1</t>
+  </si>
+  <si>
+    <t>PYAY NYEIN 2</t>
+  </si>
+  <si>
+    <t>PYAY NYEIN 3</t>
+  </si>
+  <si>
+    <t>PYAY NYEIN 4</t>
   </si>
 </sst>
 </file>
@@ -464,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3BB24B-D681-4DE8-81F7-FC89E25306BB}">
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.375" style="3" customWidth="1"/>
@@ -495,16 +495,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="7">
-        <v>1710500323889</v>
+      <c r="D2" s="5">
+        <v>69155200181078</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="7">
-        <v>1710500323889</v>
+        <v>6</v>
+      </c>
+      <c r="D3" s="5">
+        <v>69155200181078</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -529,16 +529,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="7">
-        <v>1710500323889</v>
+        <v>7</v>
+      </c>
+      <c r="D4" s="5">
+        <v>69155200181078</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -546,68 +546,26 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5">
+        <v>69155200181078</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="7">
-        <v>1710500323889</v>
-      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="7">
-        <v>1710500323889</v>
-      </c>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1710500323889</v>
-      </c>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1710500323889</v>
-      </c>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E9" s="6"/>
@@ -1034,15 +992,6 @@
     </row>
     <row r="150" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E150" s="6"/>
-    </row>
-    <row r="151" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E151" s="6"/>
-    </row>
-    <row r="152" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E152" s="6"/>
-    </row>
-    <row r="153" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E153" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/RequestData.xlsx
+++ b/RequestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\Thefirst-E-work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Desktop\E-work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2120DB0-7678-4AE7-8DE6-72955861EF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595B6C0C-33D5-41A0-A28E-6E86FCDC5518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5730" yWindow="3630" windowWidth="21600" windowHeight="11295" xr2:uid="{799AF58B-C093-4573-81AA-7B94D8971B9B}"/>
+    <workbookView xWindow="3120" yWindow="1110" windowWidth="21390" windowHeight="15090" xr2:uid="{799AF58B-C093-4573-81AA-7B94D8971B9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="7">
   <si>
     <t>ลำดับ</t>
   </si>
@@ -42,42 +53,21 @@
     <t>PASSPORT NUMBER</t>
   </si>
   <si>
-    <t>MH295863</t>
+    <t>MPM LOT 2 - 27 PAX</t>
   </si>
   <si>
-    <t>MH295864</t>
-  </si>
-  <si>
-    <t>MH295865</t>
-  </si>
-  <si>
-    <t>MH295866</t>
-  </si>
-  <si>
-    <t>Amdhr1688@gmail.com</t>
-  </si>
-  <si>
-    <t>PYAY NYEIN 1</t>
-  </si>
-  <si>
-    <t>PYAY NYEIN 2</t>
-  </si>
-  <si>
-    <t>PYAY NYEIN 3</t>
-  </si>
-  <si>
-    <t>PYAY NYEIN 4</t>
+    <t>importer168@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -86,7 +76,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -94,14 +84,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -168,9 +158,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -208,7 +198,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -314,7 +304,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -456,7 +446,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -464,16 +454,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3BB24B-D681-4DE8-81F7-FC89E25306BB}">
-  <dimension ref="A1:E150"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E147"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.375" style="3" customWidth="1"/>
-    <col min="2" max="3" width="25.125" customWidth="1"/>
-    <col min="4" max="4" width="24.375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="28.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="25.140625" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -490,508 +480,872 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="5">
-        <v>69155200181078</v>
+        <v>69144400861839</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="5">
-        <v>69155200181078</v>
+        <v>69144400861871</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5">
-        <v>69155200181078</v>
+        <v>69144400861890</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5">
+        <v>69144400861929</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5">
+        <v>69144400861941</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>69144400861959</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5">
+        <v>69144400861972</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5">
+        <v>69144400861996</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5">
+        <v>69144400862011</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>69144400862038</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5">
+        <v>69144400862057</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5">
+        <v>69144400862089</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5">
-        <v>69155200181078</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E9" s="6"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E10" s="6"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E11" s="6"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E22" s="6"/>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E23" s="6"/>
-    </row>
-    <row r="24" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E24" s="6"/>
-    </row>
-    <row r="25" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E25" s="6"/>
-    </row>
-    <row r="26" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E26" s="6"/>
-    </row>
-    <row r="27" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E27" s="6"/>
-    </row>
-    <row r="28" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E29" s="6"/>
-    </row>
-    <row r="30" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E30" s="6"/>
-    </row>
-    <row r="31" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E31" s="6"/>
-    </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E33" s="6"/>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E34" s="6"/>
-    </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E35" s="6"/>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E38" s="6"/>
-    </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E39" s="6"/>
-    </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E40" s="6"/>
-    </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5">
+        <v>69144400862118</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5">
+        <v>69144400862135</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5">
+        <v>69144400862154</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5">
+        <v>69144400862177</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="5">
+        <v>69144400862201</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="5">
+        <v>69144400862228</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5">
+        <v>69144400862245</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="5">
+        <v>69144400862281</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="5">
+        <v>69144400862302</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="5">
+        <v>69144400862328</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="5">
+        <v>69144400862356</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="5">
+        <v>69144400862384</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="5">
+        <v>69144400862421</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5">
+        <v>69144400862458</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="5">
+        <v>69144400862509</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="5">
+        <v>69144400862529</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="5">
+        <v>69144400862554</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="5">
+        <v>69144400862575</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="5">
+        <v>69144400862600</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="5">
+        <v>69144400862648</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="5">
+        <v>69144400862672</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="5">
+        <v>69144400862702</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="5">
+        <v>69144400862729</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="5">
+        <v>69144400862754</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="5">
+        <v>69144400862784</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="5">
+        <v>69144400862805</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="5">
+        <v>69144400863135</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="E41" s="6"/>
     </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="E42" s="6"/>
     </row>
-    <row r="43" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5">
       <c r="E43" s="6"/>
     </row>
-    <row r="44" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5">
       <c r="E44" s="6"/>
     </row>
-    <row r="45" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5">
       <c r="E45" s="6"/>
     </row>
-    <row r="46" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5">
       <c r="E46" s="6"/>
     </row>
-    <row r="47" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5">
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="5:5">
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="5:5">
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="5:5">
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="5:5">
       <c r="E52" s="6"/>
     </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="5:5">
       <c r="E53" s="6"/>
     </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="5:5">
       <c r="E54" s="6"/>
     </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="5:5">
       <c r="E55" s="6"/>
     </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="5:5">
       <c r="E56" s="6"/>
     </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="5:5">
       <c r="E57" s="6"/>
     </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="5:5">
       <c r="E58" s="6"/>
     </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="5:5">
       <c r="E59" s="6"/>
     </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="5:5">
       <c r="E60" s="6"/>
     </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="5:5">
       <c r="E61" s="6"/>
     </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="5:5">
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="5:5">
       <c r="E63" s="6"/>
     </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="5:5">
       <c r="E64" s="6"/>
     </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="5:5">
       <c r="E65" s="6"/>
     </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="5:5">
       <c r="E66" s="6"/>
     </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="5:5">
       <c r="E67" s="6"/>
     </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="5:5">
       <c r="E68" s="6"/>
     </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="5:5">
       <c r="E69" s="6"/>
     </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="5:5">
       <c r="E70" s="6"/>
     </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="5:5">
       <c r="E71" s="6"/>
     </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="5:5">
       <c r="E72" s="6"/>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="5:5">
       <c r="E73" s="6"/>
     </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="5:5">
       <c r="E74" s="6"/>
     </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="5:5">
       <c r="E75" s="6"/>
     </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="5:5">
       <c r="E76" s="6"/>
     </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="5:5">
       <c r="E77" s="6"/>
     </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="5:5">
       <c r="E78" s="6"/>
     </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="5:5">
       <c r="E79" s="6"/>
     </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="5:5">
       <c r="E80" s="6"/>
     </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="5:5">
       <c r="E81" s="6"/>
     </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="5:5">
       <c r="E82" s="6"/>
     </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="83" spans="5:5">
       <c r="E83" s="6"/>
     </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="84" spans="5:5">
       <c r="E84" s="6"/>
     </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="85" spans="5:5">
       <c r="E85" s="6"/>
     </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="86" spans="5:5">
       <c r="E86" s="6"/>
     </row>
-    <row r="87" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="87" spans="5:5">
       <c r="E87" s="6"/>
     </row>
-    <row r="88" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="88" spans="5:5">
       <c r="E88" s="6"/>
     </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="89" spans="5:5">
       <c r="E89" s="6"/>
     </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="90" spans="5:5">
       <c r="E90" s="6"/>
     </row>
-    <row r="91" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="91" spans="5:5">
       <c r="E91" s="6"/>
     </row>
-    <row r="92" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="92" spans="5:5">
       <c r="E92" s="6"/>
     </row>
-    <row r="93" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="93" spans="5:5">
       <c r="E93" s="6"/>
     </row>
-    <row r="94" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="94" spans="5:5">
       <c r="E94" s="6"/>
     </row>
-    <row r="95" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="95" spans="5:5">
       <c r="E95" s="6"/>
     </row>
-    <row r="96" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="96" spans="5:5">
       <c r="E96" s="6"/>
     </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:5">
       <c r="E97" s="6"/>
     </row>
-    <row r="98" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="98" spans="5:5">
       <c r="E98" s="6"/>
     </row>
-    <row r="99" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="99" spans="5:5">
       <c r="E99" s="6"/>
     </row>
-    <row r="100" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="100" spans="5:5">
       <c r="E100" s="6"/>
     </row>
-    <row r="101" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="101" spans="5:5">
       <c r="E101" s="6"/>
     </row>
-    <row r="102" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="102" spans="5:5">
       <c r="E102" s="6"/>
     </row>
-    <row r="103" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="103" spans="5:5">
       <c r="E103" s="6"/>
     </row>
-    <row r="104" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="104" spans="5:5">
       <c r="E104" s="6"/>
     </row>
-    <row r="105" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="105" spans="5:5">
       <c r="E105" s="6"/>
     </row>
-    <row r="106" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="106" spans="5:5">
       <c r="E106" s="6"/>
     </row>
-    <row r="107" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="107" spans="5:5">
       <c r="E107" s="6"/>
     </row>
-    <row r="108" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="108" spans="5:5">
       <c r="E108" s="6"/>
     </row>
-    <row r="109" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="109" spans="5:5">
       <c r="E109" s="6"/>
     </row>
-    <row r="110" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="110" spans="5:5">
       <c r="E110" s="6"/>
     </row>
-    <row r="111" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="111" spans="5:5">
       <c r="E111" s="6"/>
     </row>
-    <row r="112" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="112" spans="5:5">
       <c r="E112" s="6"/>
     </row>
-    <row r="113" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="113" spans="5:5">
       <c r="E113" s="6"/>
     </row>
-    <row r="114" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="114" spans="5:5">
       <c r="E114" s="6"/>
     </row>
-    <row r="115" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="115" spans="5:5">
       <c r="E115" s="6"/>
     </row>
-    <row r="116" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="116" spans="5:5">
       <c r="E116" s="6"/>
     </row>
-    <row r="117" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="117" spans="5:5">
       <c r="E117" s="6"/>
     </row>
-    <row r="118" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="118" spans="5:5">
       <c r="E118" s="6"/>
     </row>
-    <row r="119" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="5:5">
       <c r="E119" s="6"/>
     </row>
-    <row r="120" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="5:5">
       <c r="E120" s="6"/>
     </row>
-    <row r="121" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="5:5">
       <c r="E121" s="6"/>
     </row>
-    <row r="122" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="5:5">
       <c r="E122" s="6"/>
     </row>
-    <row r="123" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="123" spans="5:5">
       <c r="E123" s="6"/>
     </row>
-    <row r="124" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="124" spans="5:5">
       <c r="E124" s="6"/>
     </row>
-    <row r="125" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="125" spans="5:5">
       <c r="E125" s="6"/>
     </row>
-    <row r="126" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="126" spans="5:5">
       <c r="E126" s="6"/>
     </row>
-    <row r="127" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="127" spans="5:5">
       <c r="E127" s="6"/>
     </row>
-    <row r="128" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="128" spans="5:5">
       <c r="E128" s="6"/>
     </row>
-    <row r="129" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="129" spans="5:5">
       <c r="E129" s="6"/>
     </row>
-    <row r="130" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="130" spans="5:5">
       <c r="E130" s="6"/>
     </row>
-    <row r="131" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="131" spans="5:5">
       <c r="E131" s="6"/>
     </row>
-    <row r="132" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="132" spans="5:5">
       <c r="E132" s="6"/>
     </row>
-    <row r="133" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="133" spans="5:5">
       <c r="E133" s="6"/>
     </row>
-    <row r="134" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="134" spans="5:5">
       <c r="E134" s="6"/>
     </row>
-    <row r="135" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="135" spans="5:5">
       <c r="E135" s="6"/>
     </row>
-    <row r="136" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="136" spans="5:5">
       <c r="E136" s="6"/>
     </row>
-    <row r="137" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="137" spans="5:5">
       <c r="E137" s="6"/>
     </row>
-    <row r="138" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="138" spans="5:5">
       <c r="E138" s="6"/>
     </row>
-    <row r="139" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="139" spans="5:5">
       <c r="E139" s="6"/>
     </row>
-    <row r="140" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="140" spans="5:5">
       <c r="E140" s="6"/>
     </row>
-    <row r="141" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="141" spans="5:5">
       <c r="E141" s="6"/>
     </row>
-    <row r="142" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="142" spans="5:5">
       <c r="E142" s="6"/>
     </row>
-    <row r="143" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="143" spans="5:5">
       <c r="E143" s="6"/>
     </row>
-    <row r="144" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="144" spans="5:5">
       <c r="E144" s="6"/>
     </row>
-    <row r="145" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="145" spans="5:5">
       <c r="E145" s="6"/>
     </row>
-    <row r="146" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="146" spans="5:5">
       <c r="E146" s="6"/>
     </row>
-    <row r="147" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="147" spans="5:5">
       <c r="E147" s="6"/>
-    </row>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E148" s="6"/>
-    </row>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E149" s="6"/>
-    </row>
-    <row r="150" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E150" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/RequestData.xlsx
+++ b/RequestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\OneDrive\Desktop\E-work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programing\Thefirst-E-work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595B6C0C-33D5-41A0-A28E-6E86FCDC5518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D2CA09-F1CD-4D9B-A287-00150CEA9987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1110" windowWidth="21390" windowHeight="15090" xr2:uid="{799AF58B-C093-4573-81AA-7B94D8971B9B}"/>
+    <workbookView xWindow="3795" yWindow="2670" windowWidth="23760" windowHeight="10200" xr2:uid="{799AF58B-C093-4573-81AA-7B94D8971B9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>ลำดับ</t>
   </si>
@@ -53,21 +42,18 @@
     <t>PASSPORT NUMBER</t>
   </si>
   <si>
-    <t>MPM LOT 2 - 27 PAX</t>
-  </si>
-  <si>
-    <t>importer168@gmail.com</t>
+    <t>info@thefirstgoodman.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -76,7 +62,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -84,14 +70,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -158,9 +144,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -198,7 +184,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -304,7 +290,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -446,7 +432,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -455,15 +441,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3BB24B-D681-4DE8-81F7-FC89E25306BB}">
   <dimension ref="A1:E147"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" style="3" customWidth="1"/>
-    <col min="2" max="3" width="25.140625" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="7.375" style="3" customWidth="1"/>
+    <col min="2" max="3" width="25.125" customWidth="1"/>
+    <col min="4" max="4" width="24.375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="28.625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -480,876 +466,572 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="5">
+        <v>69125300062460</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="5">
-        <v>69144400861839</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="5">
-        <v>69144400861871</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="5">
-        <v>69144400861890</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="5">
-        <v>69144400861929</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="5">
-        <v>69144400861941</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="5">
-        <v>69144400861959</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="5">
-        <v>69144400861972</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="5">
-        <v>69144400861996</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="5">
-        <v>69144400862011</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="5">
-        <v>69144400862038</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="5">
-        <v>69144400862057</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="5">
-        <v>69144400862089</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="5">
-        <v>69144400862118</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="5">
-        <v>69144400862135</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="5">
-        <v>69144400862154</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="C17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="5">
-        <v>69144400862177</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="C18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="5">
-        <v>69144400862201</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="5">
-        <v>69144400862228</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="C20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="5">
-        <v>69144400862245</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="C21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="5">
-        <v>69144400862281</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>69144400862302</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="5">
-        <v>69144400862328</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="5">
-        <v>69144400862356</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="C25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="5">
-        <v>69144400862384</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="5">
-        <v>69144400862421</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="C27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="5">
-        <v>69144400862458</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="C28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="5">
-        <v>69144400862509</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="C29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="5">
-        <v>69144400862529</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="C30" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="5">
-        <v>69144400862554</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="C31" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="5">
-        <v>69144400862575</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="C32" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="5">
-        <v>69144400862600</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="C33" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="5">
-        <v>69144400862648</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="C34" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="5">
-        <v>69144400862672</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="C35" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="5">
-        <v>69144400862702</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="C36" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="5">
-        <v>69144400862729</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="C37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="5">
-        <v>69144400862754</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="C38" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="5">
-        <v>69144400862784</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="C39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="5">
-        <v>69144400862805</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="C40" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="5">
-        <v>69144400863135</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E41" s="6"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E42" s="6"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E43" s="6"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E44" s="6"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E45" s="6"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E46" s="6"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E47" s="6"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E48" s="6"/>
     </row>
-    <row r="49" spans="5:5">
+    <row r="49" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E49" s="6"/>
     </row>
-    <row r="50" spans="5:5">
+    <row r="50" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E50" s="6"/>
     </row>
-    <row r="51" spans="5:5">
+    <row r="51" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E51" s="6"/>
     </row>
-    <row r="52" spans="5:5">
+    <row r="52" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E52" s="6"/>
     </row>
-    <row r="53" spans="5:5">
+    <row r="53" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E53" s="6"/>
     </row>
-    <row r="54" spans="5:5">
+    <row r="54" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E54" s="6"/>
     </row>
-    <row r="55" spans="5:5">
+    <row r="55" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E55" s="6"/>
     </row>
-    <row r="56" spans="5:5">
+    <row r="56" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E56" s="6"/>
     </row>
-    <row r="57" spans="5:5">
+    <row r="57" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E57" s="6"/>
     </row>
-    <row r="58" spans="5:5">
+    <row r="58" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E58" s="6"/>
     </row>
-    <row r="59" spans="5:5">
+    <row r="59" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E59" s="6"/>
     </row>
-    <row r="60" spans="5:5">
+    <row r="60" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E60" s="6"/>
     </row>
-    <row r="61" spans="5:5">
+    <row r="61" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E61" s="6"/>
     </row>
-    <row r="62" spans="5:5">
+    <row r="62" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E62" s="6"/>
     </row>
-    <row r="63" spans="5:5">
+    <row r="63" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E63" s="6"/>
     </row>
-    <row r="64" spans="5:5">
+    <row r="64" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E64" s="6"/>
     </row>
-    <row r="65" spans="5:5">
+    <row r="65" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E65" s="6"/>
     </row>
-    <row r="66" spans="5:5">
+    <row r="66" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E66" s="6"/>
     </row>
-    <row r="67" spans="5:5">
+    <row r="67" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E67" s="6"/>
     </row>
-    <row r="68" spans="5:5">
+    <row r="68" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E68" s="6"/>
     </row>
-    <row r="69" spans="5:5">
+    <row r="69" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E69" s="6"/>
     </row>
-    <row r="70" spans="5:5">
+    <row r="70" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E70" s="6"/>
     </row>
-    <row r="71" spans="5:5">
+    <row r="71" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E71" s="6"/>
     </row>
-    <row r="72" spans="5:5">
+    <row r="72" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E72" s="6"/>
     </row>
-    <row r="73" spans="5:5">
+    <row r="73" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E73" s="6"/>
     </row>
-    <row r="74" spans="5:5">
+    <row r="74" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E74" s="6"/>
     </row>
-    <row r="75" spans="5:5">
+    <row r="75" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E75" s="6"/>
     </row>
-    <row r="76" spans="5:5">
+    <row r="76" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E76" s="6"/>
     </row>
-    <row r="77" spans="5:5">
+    <row r="77" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E77" s="6"/>
     </row>
-    <row r="78" spans="5:5">
+    <row r="78" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E78" s="6"/>
     </row>
-    <row r="79" spans="5:5">
+    <row r="79" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E79" s="6"/>
     </row>
-    <row r="80" spans="5:5">
+    <row r="80" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E80" s="6"/>
     </row>
-    <row r="81" spans="5:5">
+    <row r="81" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E81" s="6"/>
     </row>
-    <row r="82" spans="5:5">
+    <row r="82" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E82" s="6"/>
     </row>
-    <row r="83" spans="5:5">
+    <row r="83" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E83" s="6"/>
     </row>
-    <row r="84" spans="5:5">
+    <row r="84" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E84" s="6"/>
     </row>
-    <row r="85" spans="5:5">
+    <row r="85" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E85" s="6"/>
     </row>
-    <row r="86" spans="5:5">
+    <row r="86" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E86" s="6"/>
     </row>
-    <row r="87" spans="5:5">
+    <row r="87" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E87" s="6"/>
     </row>
-    <row r="88" spans="5:5">
+    <row r="88" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E88" s="6"/>
     </row>
-    <row r="89" spans="5:5">
+    <row r="89" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E89" s="6"/>
     </row>
-    <row r="90" spans="5:5">
+    <row r="90" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E90" s="6"/>
     </row>
-    <row r="91" spans="5:5">
+    <row r="91" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E91" s="6"/>
     </row>
-    <row r="92" spans="5:5">
+    <row r="92" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E92" s="6"/>
     </row>
-    <row r="93" spans="5:5">
+    <row r="93" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E93" s="6"/>
     </row>
-    <row r="94" spans="5:5">
+    <row r="94" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E94" s="6"/>
     </row>
-    <row r="95" spans="5:5">
+    <row r="95" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E95" s="6"/>
     </row>
-    <row r="96" spans="5:5">
+    <row r="96" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E96" s="6"/>
     </row>
-    <row r="97" spans="5:5">
+    <row r="97" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E97" s="6"/>
     </row>
-    <row r="98" spans="5:5">
+    <row r="98" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E98" s="6"/>
     </row>
-    <row r="99" spans="5:5">
+    <row r="99" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E99" s="6"/>
     </row>
-    <row r="100" spans="5:5">
+    <row r="100" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E100" s="6"/>
     </row>
-    <row r="101" spans="5:5">
+    <row r="101" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E101" s="6"/>
     </row>
-    <row r="102" spans="5:5">
+    <row r="102" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E102" s="6"/>
     </row>
-    <row r="103" spans="5:5">
+    <row r="103" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E103" s="6"/>
     </row>
-    <row r="104" spans="5:5">
+    <row r="104" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E104" s="6"/>
     </row>
-    <row r="105" spans="5:5">
+    <row r="105" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E105" s="6"/>
     </row>
-    <row r="106" spans="5:5">
+    <row r="106" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E106" s="6"/>
     </row>
-    <row r="107" spans="5:5">
+    <row r="107" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E107" s="6"/>
     </row>
-    <row r="108" spans="5:5">
+    <row r="108" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E108" s="6"/>
     </row>
-    <row r="109" spans="5:5">
+    <row r="109" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E109" s="6"/>
     </row>
-    <row r="110" spans="5:5">
+    <row r="110" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E110" s="6"/>
     </row>
-    <row r="111" spans="5:5">
+    <row r="111" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E111" s="6"/>
     </row>
-    <row r="112" spans="5:5">
+    <row r="112" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E112" s="6"/>
     </row>
-    <row r="113" spans="5:5">
+    <row r="113" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E113" s="6"/>
     </row>
-    <row r="114" spans="5:5">
+    <row r="114" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E114" s="6"/>
     </row>
-    <row r="115" spans="5:5">
+    <row r="115" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E115" s="6"/>
     </row>
-    <row r="116" spans="5:5">
+    <row r="116" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E116" s="6"/>
     </row>
-    <row r="117" spans="5:5">
+    <row r="117" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E117" s="6"/>
     </row>
-    <row r="118" spans="5:5">
+    <row r="118" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E118" s="6"/>
     </row>
-    <row r="119" spans="5:5">
+    <row r="119" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E119" s="6"/>
     </row>
-    <row r="120" spans="5:5">
+    <row r="120" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E120" s="6"/>
     </row>
-    <row r="121" spans="5:5">
+    <row r="121" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E121" s="6"/>
     </row>
-    <row r="122" spans="5:5">
+    <row r="122" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E122" s="6"/>
     </row>
-    <row r="123" spans="5:5">
+    <row r="123" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E123" s="6"/>
     </row>
-    <row r="124" spans="5:5">
+    <row r="124" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E124" s="6"/>
     </row>
-    <row r="125" spans="5:5">
+    <row r="125" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E125" s="6"/>
     </row>
-    <row r="126" spans="5:5">
+    <row r="126" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E126" s="6"/>
     </row>
-    <row r="127" spans="5:5">
+    <row r="127" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E127" s="6"/>
     </row>
-    <row r="128" spans="5:5">
+    <row r="128" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E128" s="6"/>
     </row>
-    <row r="129" spans="5:5">
+    <row r="129" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E129" s="6"/>
     </row>
-    <row r="130" spans="5:5">
+    <row r="130" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E130" s="6"/>
     </row>
-    <row r="131" spans="5:5">
+    <row r="131" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E131" s="6"/>
     </row>
-    <row r="132" spans="5:5">
+    <row r="132" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E132" s="6"/>
     </row>
-    <row r="133" spans="5:5">
+    <row r="133" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E133" s="6"/>
     </row>
-    <row r="134" spans="5:5">
+    <row r="134" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E134" s="6"/>
     </row>
-    <row r="135" spans="5:5">
+    <row r="135" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E135" s="6"/>
     </row>
-    <row r="136" spans="5:5">
+    <row r="136" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E136" s="6"/>
     </row>
-    <row r="137" spans="5:5">
+    <row r="137" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E137" s="6"/>
     </row>
-    <row r="138" spans="5:5">
+    <row r="138" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E138" s="6"/>
     </row>
-    <row r="139" spans="5:5">
+    <row r="139" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E139" s="6"/>
     </row>
-    <row r="140" spans="5:5">
+    <row r="140" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E140" s="6"/>
     </row>
-    <row r="141" spans="5:5">
+    <row r="141" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E141" s="6"/>
     </row>
-    <row r="142" spans="5:5">
+    <row r="142" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E142" s="6"/>
     </row>
-    <row r="143" spans="5:5">
+    <row r="143" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E143" s="6"/>
     </row>
-    <row r="144" spans="5:5">
+    <row r="144" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E144" s="6"/>
     </row>
-    <row r="145" spans="5:5">
+    <row r="145" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E145" s="6"/>
     </row>
-    <row r="146" spans="5:5">
+    <row r="146" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E146" s="6"/>
     </row>
-    <row r="147" spans="5:5">
+    <row r="147" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E147" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{CB8EC0BD-56B0-43BA-8A68-6AA5C99E38E6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>